--- a/misc/全nameとid.xlsx
+++ b/misc/全nameとid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A5214-FA2A-4DF1-884A-7D6BEB1A3650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91849AE-80F4-4D48-B2D9-B31BDCFC13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10376,7 +10376,7 @@
         <v>663</v>
       </c>
       <c r="B250">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="C250" t="s">
         <v>638</v>
@@ -10416,7 +10416,7 @@
         <v>663</v>
       </c>
       <c r="B252">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="C252" t="s">
         <v>640</v>
@@ -11157,7 +11157,7 @@
   </sheetData>
   <phoneticPr fontId="5"/>
   <conditionalFormatting sqref="C236">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="渡辺">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="渡辺">
       <formula>NOT(ISERROR(SEARCH("渡辺",C236)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11216,7 +11216,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <f>_xlfn.XLOOKUP(E2, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F2:F33" si="0">_xlfn.XLOOKUP(E2, B$2:B$231, A$2:A$231, 0)</f>
         <v>1</v>
       </c>
       <c r="G2">
@@ -11240,7 +11240,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <f>_xlfn.XLOOKUP(E3, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="G3">
@@ -11264,7 +11264,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <f>_xlfn.XLOOKUP(E4, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="G4">
@@ -11288,7 +11288,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <f>_xlfn.XLOOKUP(E5, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G5">
@@ -11312,7 +11312,7 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <f>_xlfn.XLOOKUP(E6, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="G6">
@@ -11336,7 +11336,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <f>_xlfn.XLOOKUP(E7, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="G7">
@@ -11360,7 +11360,7 @@
         <v>7</v>
       </c>
       <c r="F8">
-        <f>_xlfn.XLOOKUP(E8, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="G8">
@@ -11384,7 +11384,7 @@
         <v>8</v>
       </c>
       <c r="F9">
-        <f>_xlfn.XLOOKUP(E9, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="G9">
@@ -11408,7 +11408,7 @@
         <v>9</v>
       </c>
       <c r="F10">
-        <f>_xlfn.XLOOKUP(E10, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="G10">
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <f>_xlfn.XLOOKUP(E11, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G11">
@@ -11456,7 +11456,7 @@
         <v>11</v>
       </c>
       <c r="F12">
-        <f>_xlfn.XLOOKUP(E12, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="G12">
@@ -11480,7 +11480,7 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <f>_xlfn.XLOOKUP(E13, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="G13">
@@ -11504,7 +11504,7 @@
         <v>13</v>
       </c>
       <c r="F14">
-        <f>_xlfn.XLOOKUP(E14, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="G14">
@@ -11528,7 +11528,7 @@
         <v>14</v>
       </c>
       <c r="F15">
-        <f>_xlfn.XLOOKUP(E15, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="G15">
@@ -11552,7 +11552,7 @@
         <v>15</v>
       </c>
       <c r="F16">
-        <f>_xlfn.XLOOKUP(E16, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="G16">
@@ -11576,7 +11576,7 @@
         <v>17</v>
       </c>
       <c r="F17">
-        <f>_xlfn.XLOOKUP(E17, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="G17">
@@ -11600,7 +11600,7 @@
         <v>18</v>
       </c>
       <c r="F18">
-        <f>_xlfn.XLOOKUP(E18, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="G18">
@@ -11624,7 +11624,7 @@
         <v>19</v>
       </c>
       <c r="F19">
-        <f>_xlfn.XLOOKUP(E19, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="G19">
@@ -11648,7 +11648,7 @@
         <v>20</v>
       </c>
       <c r="F20">
-        <f>_xlfn.XLOOKUP(E20, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="G20">
@@ -11672,7 +11672,7 @@
         <v>21</v>
       </c>
       <c r="F21">
-        <f>_xlfn.XLOOKUP(E21, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="G21">
@@ -11696,7 +11696,7 @@
         <v>22</v>
       </c>
       <c r="F22">
-        <f>_xlfn.XLOOKUP(E22, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="G22">
@@ -11720,7 +11720,7 @@
         <v>23</v>
       </c>
       <c r="F23">
-        <f>_xlfn.XLOOKUP(E23, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="G23">
@@ -11744,7 +11744,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <f>_xlfn.XLOOKUP(E24, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="G24">
@@ -11768,7 +11768,7 @@
         <v>26</v>
       </c>
       <c r="F25">
-        <f>_xlfn.XLOOKUP(E25, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="G25">
@@ -11792,7 +11792,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <f>_xlfn.XLOOKUP(E26, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="G26">
@@ -11816,7 +11816,7 @@
         <v>28</v>
       </c>
       <c r="F27">
-        <f>_xlfn.XLOOKUP(E27, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="G27">
@@ -11840,7 +11840,7 @@
         <v>30</v>
       </c>
       <c r="F28">
-        <f>_xlfn.XLOOKUP(E28, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="G28">
@@ -11864,7 +11864,7 @@
         <v>32</v>
       </c>
       <c r="F29">
-        <f>_xlfn.XLOOKUP(E29, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="G29">
@@ -11888,7 +11888,7 @@
         <v>34</v>
       </c>
       <c r="F30">
-        <f>_xlfn.XLOOKUP(E30, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="G30">
@@ -11912,7 +11912,7 @@
         <v>35</v>
       </c>
       <c r="F31">
-        <f>_xlfn.XLOOKUP(E31, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="G31">
@@ -11936,7 +11936,7 @@
         <v>36</v>
       </c>
       <c r="F32">
-        <f>_xlfn.XLOOKUP(E32, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="G32">
@@ -11960,7 +11960,7 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <f>_xlfn.XLOOKUP(E33, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="G33">
@@ -11984,7 +11984,7 @@
         <v>38</v>
       </c>
       <c r="F34">
-        <f>_xlfn.XLOOKUP(E34, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F34:F65" si="1">_xlfn.XLOOKUP(E34, B$2:B$231, A$2:A$231, 0)</f>
         <v>38</v>
       </c>
       <c r="G34">
@@ -12008,7 +12008,7 @@
         <v>39</v>
       </c>
       <c r="F35">
-        <f>_xlfn.XLOOKUP(E35, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="G35">
@@ -12032,7 +12032,7 @@
         <v>40</v>
       </c>
       <c r="F36">
-        <f>_xlfn.XLOOKUP(E36, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="G36">
@@ -12056,7 +12056,7 @@
         <v>41</v>
       </c>
       <c r="F37">
-        <f>_xlfn.XLOOKUP(E37, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="G37">
@@ -12080,7 +12080,7 @@
         <v>44</v>
       </c>
       <c r="F38">
-        <f>_xlfn.XLOOKUP(E38, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="G38">
@@ -12104,7 +12104,7 @@
         <v>45</v>
       </c>
       <c r="F39">
-        <f>_xlfn.XLOOKUP(E39, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="G39">
@@ -12128,7 +12128,7 @@
         <v>46</v>
       </c>
       <c r="F40">
-        <f>_xlfn.XLOOKUP(E40, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="G40">
@@ -12152,7 +12152,7 @@
         <v>47</v>
       </c>
       <c r="F41">
-        <f>_xlfn.XLOOKUP(E41, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="G41">
@@ -12176,7 +12176,7 @@
         <v>48</v>
       </c>
       <c r="F42">
-        <f>_xlfn.XLOOKUP(E42, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="G42">
@@ -12200,7 +12200,7 @@
         <v>49</v>
       </c>
       <c r="F43">
-        <f>_xlfn.XLOOKUP(E43, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="G43">
@@ -12224,7 +12224,7 @@
         <v>50</v>
       </c>
       <c r="F44">
-        <f>_xlfn.XLOOKUP(E44, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="G44">
@@ -12248,7 +12248,7 @@
         <v>51</v>
       </c>
       <c r="F45">
-        <f>_xlfn.XLOOKUP(E45, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="G45">
@@ -12272,7 +12272,7 @@
         <v>52</v>
       </c>
       <c r="F46">
-        <f>_xlfn.XLOOKUP(E46, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="G46">
@@ -12296,7 +12296,7 @@
         <v>53</v>
       </c>
       <c r="F47">
-        <f>_xlfn.XLOOKUP(E47, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="G47">
@@ -12320,7 +12320,7 @@
         <v>54</v>
       </c>
       <c r="F48">
-        <f>_xlfn.XLOOKUP(E48, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="G48">
@@ -12344,7 +12344,7 @@
         <v>55</v>
       </c>
       <c r="F49">
-        <f>_xlfn.XLOOKUP(E49, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="G49">
@@ -12368,7 +12368,7 @@
         <v>56</v>
       </c>
       <c r="F50">
-        <f>_xlfn.XLOOKUP(E50, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="G50">
@@ -12392,7 +12392,7 @@
         <v>57</v>
       </c>
       <c r="F51">
-        <f>_xlfn.XLOOKUP(E51, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="G51">
@@ -12416,7 +12416,7 @@
         <v>60</v>
       </c>
       <c r="F52">
-        <f>_xlfn.XLOOKUP(E52, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="G52">
@@ -12440,7 +12440,7 @@
         <v>62</v>
       </c>
       <c r="F53">
-        <f>_xlfn.XLOOKUP(E53, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="G53">
@@ -12464,7 +12464,7 @@
         <v>64</v>
       </c>
       <c r="F54">
-        <f>_xlfn.XLOOKUP(E54, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="G54">
@@ -12488,7 +12488,7 @@
         <v>66</v>
       </c>
       <c r="F55">
-        <f>_xlfn.XLOOKUP(E55, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="G55">
@@ -12512,7 +12512,7 @@
         <v>67</v>
       </c>
       <c r="F56">
-        <f>_xlfn.XLOOKUP(E56, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="G56">
@@ -12536,7 +12536,7 @@
         <v>71</v>
       </c>
       <c r="F57">
-        <f>_xlfn.XLOOKUP(E57, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="G57">
@@ -12560,7 +12560,7 @@
         <v>73</v>
       </c>
       <c r="F58">
-        <f>_xlfn.XLOOKUP(E58, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="G58">
@@ -12584,7 +12584,7 @@
         <v>74</v>
       </c>
       <c r="F59">
-        <f>_xlfn.XLOOKUP(E59, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="G59">
@@ -12608,7 +12608,7 @@
         <v>75</v>
       </c>
       <c r="F60">
-        <f>_xlfn.XLOOKUP(E60, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="G60">
@@ -12632,7 +12632,7 @@
         <v>77</v>
       </c>
       <c r="F61">
-        <f>_xlfn.XLOOKUP(E61, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="G61">
@@ -12656,7 +12656,7 @@
         <v>78</v>
       </c>
       <c r="F62">
-        <f>_xlfn.XLOOKUP(E62, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="G62">
@@ -12680,7 +12680,7 @@
         <v>79</v>
       </c>
       <c r="F63">
-        <f>_xlfn.XLOOKUP(E63, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="G63">
@@ -12704,7 +12704,7 @@
         <v>82</v>
       </c>
       <c r="F64">
-        <f>_xlfn.XLOOKUP(E64, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="G64">
@@ -12728,7 +12728,7 @@
         <v>88</v>
       </c>
       <c r="F65">
-        <f>_xlfn.XLOOKUP(E65, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="G65">
@@ -12752,7 +12752,7 @@
         <v>90</v>
       </c>
       <c r="F66">
-        <f>_xlfn.XLOOKUP(E66, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F66:F97" si="2">_xlfn.XLOOKUP(E66, B$2:B$231, A$2:A$231, 0)</f>
         <v>90</v>
       </c>
       <c r="G66">
@@ -12776,7 +12776,7 @@
         <v>93</v>
       </c>
       <c r="F67">
-        <f>_xlfn.XLOOKUP(E67, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="G67">
@@ -12800,7 +12800,7 @@
         <v>94</v>
       </c>
       <c r="F68">
-        <f>_xlfn.XLOOKUP(E68, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="G68">
@@ -12824,7 +12824,7 @@
         <v>95</v>
       </c>
       <c r="F69">
-        <f>_xlfn.XLOOKUP(E69, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="G69">
@@ -12848,7 +12848,7 @@
         <v>97</v>
       </c>
       <c r="F70">
-        <f>_xlfn.XLOOKUP(E70, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="G70">
@@ -12872,7 +12872,7 @@
         <v>99</v>
       </c>
       <c r="F71">
-        <f>_xlfn.XLOOKUP(E71, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="G71">
@@ -12896,7 +12896,7 @@
         <v>244</v>
       </c>
       <c r="F72">
-        <f>_xlfn.XLOOKUP(E72, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="G72">
@@ -12920,7 +12920,7 @@
         <v>101</v>
       </c>
       <c r="F73">
-        <f>_xlfn.XLOOKUP(E73, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="G73">
@@ -12944,7 +12944,7 @@
         <v>109</v>
       </c>
       <c r="F74">
-        <f>_xlfn.XLOOKUP(E74, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="G74">
@@ -12968,7 +12968,7 @@
         <v>110</v>
       </c>
       <c r="F75">
-        <f>_xlfn.XLOOKUP(E75, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="G75">
@@ -12992,7 +12992,7 @@
         <v>114</v>
       </c>
       <c r="F76">
-        <f>_xlfn.XLOOKUP(E76, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>114</v>
       </c>
       <c r="G76">
@@ -13016,7 +13016,7 @@
         <v>115</v>
       </c>
       <c r="F77">
-        <f>_xlfn.XLOOKUP(E77, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="G77">
@@ -13040,7 +13040,7 @@
         <v>116</v>
       </c>
       <c r="F78">
-        <f>_xlfn.XLOOKUP(E78, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="G78">
@@ -13064,7 +13064,7 @@
         <v>117</v>
       </c>
       <c r="F79">
-        <f>_xlfn.XLOOKUP(E79, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="G79">
@@ -13088,7 +13088,7 @@
         <v>118</v>
       </c>
       <c r="F80">
-        <f>_xlfn.XLOOKUP(E80, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>118</v>
       </c>
       <c r="G80">
@@ -13112,7 +13112,7 @@
         <v>119</v>
       </c>
       <c r="F81">
-        <f>_xlfn.XLOOKUP(E81, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="G81">
@@ -13136,7 +13136,7 @@
         <v>120</v>
       </c>
       <c r="F82">
-        <f>_xlfn.XLOOKUP(E82, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="G82">
@@ -13160,7 +13160,7 @@
         <v>121</v>
       </c>
       <c r="F83">
-        <f>_xlfn.XLOOKUP(E83, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="G83">
@@ -13184,7 +13184,7 @@
         <v>122</v>
       </c>
       <c r="F84">
-        <f>_xlfn.XLOOKUP(E84, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="G84">
@@ -13208,7 +13208,7 @@
         <v>123</v>
       </c>
       <c r="F85">
-        <f>_xlfn.XLOOKUP(E85, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>123</v>
       </c>
       <c r="G85">
@@ -13232,7 +13232,7 @@
         <v>124</v>
       </c>
       <c r="F86">
-        <f>_xlfn.XLOOKUP(E86, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>124</v>
       </c>
       <c r="G86">
@@ -13256,7 +13256,7 @@
         <v>126</v>
       </c>
       <c r="F87">
-        <f>_xlfn.XLOOKUP(E87, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="G87">
@@ -13280,7 +13280,7 @@
         <v>127</v>
       </c>
       <c r="F88">
-        <f>_xlfn.XLOOKUP(E88, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>127</v>
       </c>
       <c r="G88">
@@ -13304,7 +13304,7 @@
         <v>128</v>
       </c>
       <c r="F89">
-        <f>_xlfn.XLOOKUP(E89, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>128</v>
       </c>
       <c r="G89">
@@ -13328,7 +13328,7 @@
         <v>129</v>
       </c>
       <c r="F90">
-        <f>_xlfn.XLOOKUP(E90, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>129</v>
       </c>
       <c r="G90">
@@ -13352,7 +13352,7 @@
         <v>130</v>
       </c>
       <c r="F91">
-        <f>_xlfn.XLOOKUP(E91, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="G91">
@@ -13376,7 +13376,7 @@
         <v>132</v>
       </c>
       <c r="F92">
-        <f>_xlfn.XLOOKUP(E92, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="G92">
@@ -13400,7 +13400,7 @@
         <v>133</v>
       </c>
       <c r="F93">
-        <f>_xlfn.XLOOKUP(E93, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="G93">
@@ -13424,7 +13424,7 @@
         <v>134</v>
       </c>
       <c r="F94">
-        <f>_xlfn.XLOOKUP(E94, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="G94">
@@ -13448,7 +13448,7 @@
         <v>136</v>
       </c>
       <c r="F95">
-        <f>_xlfn.XLOOKUP(E95, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="G95">
@@ -13472,7 +13472,7 @@
         <v>137</v>
       </c>
       <c r="F96">
-        <f>_xlfn.XLOOKUP(E96, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="G96">
@@ -13496,7 +13496,7 @@
         <v>138</v>
       </c>
       <c r="F97">
-        <f>_xlfn.XLOOKUP(E97, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="G97">
@@ -13520,7 +13520,7 @@
         <v>233</v>
       </c>
       <c r="F98">
-        <f>_xlfn.XLOOKUP(E98, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F98:F129" si="3">_xlfn.XLOOKUP(E98, B$2:B$231, A$2:A$231, 0)</f>
         <v>139</v>
       </c>
       <c r="G98">
@@ -13544,7 +13544,7 @@
         <v>141</v>
       </c>
       <c r="F99">
-        <f>_xlfn.XLOOKUP(E99, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>141</v>
       </c>
       <c r="G99">
@@ -13568,7 +13568,7 @@
         <v>142</v>
       </c>
       <c r="F100">
-        <f>_xlfn.XLOOKUP(E100, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>142</v>
       </c>
       <c r="G100">
@@ -13592,7 +13592,7 @@
         <v>143</v>
       </c>
       <c r="F101">
-        <f>_xlfn.XLOOKUP(E101, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>143</v>
       </c>
       <c r="G101">
@@ -13616,7 +13616,7 @@
         <v>144</v>
       </c>
       <c r="F102">
-        <f>_xlfn.XLOOKUP(E102, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>144</v>
       </c>
       <c r="G102">
@@ -13640,7 +13640,7 @@
         <v>145</v>
       </c>
       <c r="F103">
-        <f>_xlfn.XLOOKUP(E103, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>145</v>
       </c>
       <c r="G103">
@@ -13664,7 +13664,7 @@
         <v>146</v>
       </c>
       <c r="F104">
-        <f>_xlfn.XLOOKUP(E104, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>146</v>
       </c>
       <c r="G104">
@@ -13688,7 +13688,7 @@
         <v>147</v>
       </c>
       <c r="F105">
-        <f>_xlfn.XLOOKUP(E105, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>147</v>
       </c>
       <c r="G105">
@@ -13712,7 +13712,7 @@
         <v>148</v>
       </c>
       <c r="F106">
-        <f>_xlfn.XLOOKUP(E106, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>148</v>
       </c>
       <c r="G106">
@@ -13736,7 +13736,7 @@
         <v>151</v>
       </c>
       <c r="F107">
-        <f>_xlfn.XLOOKUP(E107, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>151</v>
       </c>
       <c r="G107">
@@ -13760,7 +13760,7 @@
         <v>152</v>
       </c>
       <c r="F108">
-        <f>_xlfn.XLOOKUP(E108, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>152</v>
       </c>
       <c r="G108">
@@ -13784,7 +13784,7 @@
         <v>153</v>
       </c>
       <c r="F109">
-        <f>_xlfn.XLOOKUP(E109, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>153</v>
       </c>
       <c r="G109">
@@ -13808,7 +13808,7 @@
         <v>154</v>
       </c>
       <c r="F110">
-        <f>_xlfn.XLOOKUP(E110, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>154</v>
       </c>
       <c r="G110">
@@ -13832,7 +13832,7 @@
         <v>155</v>
       </c>
       <c r="F111">
-        <f>_xlfn.XLOOKUP(E111, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>155</v>
       </c>
       <c r="G111">
@@ -13856,7 +13856,7 @@
         <v>156</v>
       </c>
       <c r="F112">
-        <f>_xlfn.XLOOKUP(E112, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>156</v>
       </c>
       <c r="G112">
@@ -13880,7 +13880,7 @@
         <v>157</v>
       </c>
       <c r="F113">
-        <f>_xlfn.XLOOKUP(E113, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>157</v>
       </c>
       <c r="G113">
@@ -13904,7 +13904,7 @@
         <v>158</v>
       </c>
       <c r="F114">
-        <f>_xlfn.XLOOKUP(E114, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>158</v>
       </c>
       <c r="G114">
@@ -13928,7 +13928,7 @@
         <v>159</v>
       </c>
       <c r="F115">
-        <f>_xlfn.XLOOKUP(E115, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>159</v>
       </c>
       <c r="G115">
@@ -13952,7 +13952,7 @@
         <v>160</v>
       </c>
       <c r="F116">
-        <f>_xlfn.XLOOKUP(E116, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>160</v>
       </c>
       <c r="G116">
@@ -13976,7 +13976,7 @@
         <v>162</v>
       </c>
       <c r="F117">
-        <f>_xlfn.XLOOKUP(E117, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>162</v>
       </c>
       <c r="G117">
@@ -14000,7 +14000,7 @@
         <v>164</v>
       </c>
       <c r="F118">
-        <f>_xlfn.XLOOKUP(E118, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>164</v>
       </c>
       <c r="G118">
@@ -14024,7 +14024,7 @@
         <v>166</v>
       </c>
       <c r="F119">
-        <f>_xlfn.XLOOKUP(E119, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>166</v>
       </c>
       <c r="G119">
@@ -14048,7 +14048,7 @@
         <v>167</v>
       </c>
       <c r="F120">
-        <f>_xlfn.XLOOKUP(E120, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>167</v>
       </c>
       <c r="G120">
@@ -14072,7 +14072,7 @@
         <v>168</v>
       </c>
       <c r="F121">
-        <f>_xlfn.XLOOKUP(E121, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>168</v>
       </c>
       <c r="G121">
@@ -14096,7 +14096,7 @@
         <v>170</v>
       </c>
       <c r="F122">
-        <f>_xlfn.XLOOKUP(E122, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>170</v>
       </c>
       <c r="G122">
@@ -14120,7 +14120,7 @@
         <v>171</v>
       </c>
       <c r="F123">
-        <f>_xlfn.XLOOKUP(E123, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>171</v>
       </c>
       <c r="G123">
@@ -14144,7 +14144,7 @@
         <v>172</v>
       </c>
       <c r="F124">
-        <f>_xlfn.XLOOKUP(E124, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>172</v>
       </c>
       <c r="G124">
@@ -14168,7 +14168,7 @@
         <v>173</v>
       </c>
       <c r="F125">
-        <f>_xlfn.XLOOKUP(E125, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>173</v>
       </c>
       <c r="G125">
@@ -14192,7 +14192,7 @@
         <v>174</v>
       </c>
       <c r="F126">
-        <f>_xlfn.XLOOKUP(E126, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>174</v>
       </c>
       <c r="G126">
@@ -14216,7 +14216,7 @@
         <v>175</v>
       </c>
       <c r="F127">
-        <f>_xlfn.XLOOKUP(E127, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>175</v>
       </c>
       <c r="G127">
@@ -14240,7 +14240,7 @@
         <v>176</v>
       </c>
       <c r="F128">
-        <f>_xlfn.XLOOKUP(E128, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>176</v>
       </c>
       <c r="G128">
@@ -14264,7 +14264,7 @@
         <v>177</v>
       </c>
       <c r="F129">
-        <f>_xlfn.XLOOKUP(E129, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="3"/>
         <v>177</v>
       </c>
       <c r="G129">
@@ -14288,7 +14288,7 @@
         <v>179</v>
       </c>
       <c r="F130">
-        <f>_xlfn.XLOOKUP(E130, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F130:F161" si="4">_xlfn.XLOOKUP(E130, B$2:B$231, A$2:A$231, 0)</f>
         <v>179</v>
       </c>
       <c r="G130">
@@ -14312,7 +14312,7 @@
         <v>181</v>
       </c>
       <c r="F131">
-        <f>_xlfn.XLOOKUP(E131, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>181</v>
       </c>
       <c r="G131">
@@ -14336,7 +14336,7 @@
         <v>182</v>
       </c>
       <c r="F132">
-        <f>_xlfn.XLOOKUP(E132, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>182</v>
       </c>
       <c r="G132">
@@ -14360,7 +14360,7 @@
         <v>183</v>
       </c>
       <c r="F133">
-        <f>_xlfn.XLOOKUP(E133, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>183</v>
       </c>
       <c r="G133">
@@ -14384,7 +14384,7 @@
         <v>185</v>
       </c>
       <c r="F134">
-        <f>_xlfn.XLOOKUP(E134, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>185</v>
       </c>
       <c r="G134">
@@ -14408,7 +14408,7 @@
         <v>186</v>
       </c>
       <c r="F135">
-        <f>_xlfn.XLOOKUP(E135, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>186</v>
       </c>
       <c r="G135">
@@ -14432,7 +14432,7 @@
         <v>187</v>
       </c>
       <c r="F136">
-        <f>_xlfn.XLOOKUP(E136, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>187</v>
       </c>
       <c r="G136">
@@ -14456,7 +14456,7 @@
         <v>189</v>
       </c>
       <c r="F137">
-        <f>_xlfn.XLOOKUP(E137, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>189</v>
       </c>
       <c r="G137">
@@ -14480,7 +14480,7 @@
         <v>190</v>
       </c>
       <c r="F138">
-        <f>_xlfn.XLOOKUP(E138, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>190</v>
       </c>
       <c r="G138">
@@ -14504,7 +14504,7 @@
         <v>191</v>
       </c>
       <c r="F139">
-        <f>_xlfn.XLOOKUP(E139, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>191</v>
       </c>
       <c r="G139">
@@ -14528,7 +14528,7 @@
         <v>192</v>
       </c>
       <c r="F140">
-        <f>_xlfn.XLOOKUP(E140, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>192</v>
       </c>
       <c r="G140">
@@ -14552,7 +14552,7 @@
         <v>193</v>
       </c>
       <c r="F141">
-        <f>_xlfn.XLOOKUP(E141, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>193</v>
       </c>
       <c r="G141">
@@ -14576,7 +14576,7 @@
         <v>194</v>
       </c>
       <c r="F142">
-        <f>_xlfn.XLOOKUP(E142, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>194</v>
       </c>
       <c r="G142">
@@ -14600,7 +14600,7 @@
         <v>195</v>
       </c>
       <c r="F143">
-        <f>_xlfn.XLOOKUP(E143, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>195</v>
       </c>
       <c r="G143">
@@ -14624,7 +14624,7 @@
         <v>196</v>
       </c>
       <c r="F144">
-        <f>_xlfn.XLOOKUP(E144, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>196</v>
       </c>
       <c r="G144">
@@ -14648,7 +14648,7 @@
         <v>197</v>
       </c>
       <c r="F145">
-        <f>_xlfn.XLOOKUP(E145, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>197</v>
       </c>
       <c r="G145">
@@ -14672,7 +14672,7 @@
         <v>198</v>
       </c>
       <c r="F146">
-        <f>_xlfn.XLOOKUP(E146, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>198</v>
       </c>
       <c r="G146">
@@ -14696,7 +14696,7 @@
         <v>199</v>
       </c>
       <c r="F147">
-        <f>_xlfn.XLOOKUP(E147, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>199</v>
       </c>
       <c r="G147">
@@ -14720,7 +14720,7 @@
         <v>201</v>
       </c>
       <c r="F148">
-        <f>_xlfn.XLOOKUP(E148, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>201</v>
       </c>
       <c r="G148">
@@ -14744,7 +14744,7 @@
         <v>203</v>
       </c>
       <c r="F149">
-        <f>_xlfn.XLOOKUP(E149, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>203</v>
       </c>
       <c r="G149">
@@ -14768,7 +14768,7 @@
         <v>204</v>
       </c>
       <c r="F150">
-        <f>_xlfn.XLOOKUP(E150, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>204</v>
       </c>
       <c r="G150">
@@ -14792,7 +14792,7 @@
         <v>205</v>
       </c>
       <c r="F151">
-        <f>_xlfn.XLOOKUP(E151, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>205</v>
       </c>
       <c r="G151">
@@ -14816,7 +14816,7 @@
         <v>206</v>
       </c>
       <c r="F152">
-        <f>_xlfn.XLOOKUP(E152, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>206</v>
       </c>
       <c r="G152">
@@ -14840,7 +14840,7 @@
         <v>209</v>
       </c>
       <c r="F153">
-        <f>_xlfn.XLOOKUP(E153, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>209</v>
       </c>
       <c r="G153">
@@ -14864,7 +14864,7 @@
         <v>210</v>
       </c>
       <c r="F154">
-        <f>_xlfn.XLOOKUP(E154, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>210</v>
       </c>
       <c r="G154">
@@ -14888,7 +14888,7 @@
         <v>211</v>
       </c>
       <c r="F155">
-        <f>_xlfn.XLOOKUP(E155, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>211</v>
       </c>
       <c r="G155">
@@ -14912,7 +14912,7 @@
         <v>212</v>
       </c>
       <c r="F156">
-        <f>_xlfn.XLOOKUP(E156, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>212</v>
       </c>
       <c r="G156">
@@ -14936,7 +14936,7 @@
         <v>214</v>
       </c>
       <c r="F157">
-        <f>_xlfn.XLOOKUP(E157, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>214</v>
       </c>
       <c r="G157">
@@ -14960,7 +14960,7 @@
         <v>215</v>
       </c>
       <c r="F158">
-        <f>_xlfn.XLOOKUP(E158, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>215</v>
       </c>
       <c r="G158">
@@ -14984,7 +14984,7 @@
         <v>220</v>
       </c>
       <c r="F159">
-        <f>_xlfn.XLOOKUP(E159, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>220</v>
       </c>
       <c r="G159">
@@ -15008,7 +15008,7 @@
         <v>221</v>
       </c>
       <c r="F160">
-        <f>_xlfn.XLOOKUP(E160, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>221</v>
       </c>
       <c r="G160">
@@ -15032,7 +15032,7 @@
         <v>222</v>
       </c>
       <c r="F161">
-        <f>_xlfn.XLOOKUP(E161, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="4"/>
         <v>222</v>
       </c>
       <c r="G161">
@@ -15056,7 +15056,7 @@
         <v>224</v>
       </c>
       <c r="F162">
-        <f>_xlfn.XLOOKUP(E162, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" ref="F162:F193" si="5">_xlfn.XLOOKUP(E162, B$2:B$231, A$2:A$231, 0)</f>
         <v>224</v>
       </c>
       <c r="G162">
@@ -15080,7 +15080,7 @@
         <v>225</v>
       </c>
       <c r="F163">
-        <f>_xlfn.XLOOKUP(E163, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="5"/>
         <v>225</v>
       </c>
       <c r="G163">
@@ -15104,7 +15104,7 @@
         <v>226</v>
       </c>
       <c r="F164">
-        <f>_xlfn.XLOOKUP(E164, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="5"/>
         <v>226</v>
       </c>
       <c r="G164">
@@ -15128,7 +15128,7 @@
         <v>227</v>
       </c>
       <c r="F165">
-        <f>_xlfn.XLOOKUP(E165, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="5"/>
         <v>227</v>
       </c>
       <c r="G165">
@@ -15152,7 +15152,7 @@
         <v>229</v>
       </c>
       <c r="F166">
-        <f>_xlfn.XLOOKUP(E166, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="5"/>
         <v>229</v>
       </c>
       <c r="G166">
@@ -15176,7 +15176,7 @@
         <v>230</v>
       </c>
       <c r="F167">
-        <f>_xlfn.XLOOKUP(E167, B$2:B$231, A$2:A$231, 0)</f>
+        <f t="shared" si="5"/>
         <v>230</v>
       </c>
       <c r="G167">
@@ -16018,7 +16018,7 @@
   </autoFilter>
   <phoneticPr fontId="5"/>
   <conditionalFormatting sqref="E172">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="渡辺">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="渡辺">
       <formula>NOT(ISERROR(SEARCH("渡辺",E172)))</formula>
     </cfRule>
   </conditionalFormatting>
